--- a/etf_holdings/2026-09-01_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -522,12 +522,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>8.65%1,034,000</t>
+          <t>8.58%1,034,000</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>8.65%</t>
+          <t>8.58%</t>
         </is>
       </c>
       <c r="K2" t="n">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -583,12 +583,12 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>6.42%470,000</t>
+          <t>6.90%470,000</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>6.42%</t>
+          <t>6.90%</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -596,7 +596,7 @@
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>+0.60%</t>
+          <t>+0.64%</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -644,12 +644,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.07%123,000</t>
+          <t>5.92%123,000</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>6.07%</t>
+          <t>5.92%</t>
         </is>
       </c>
       <c r="K4" t="n">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -705,12 +705,12 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.45%221,000</t>
+          <t>5.86%221,000</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.45%</t>
+          <t>5.86%</t>
         </is>
       </c>
       <c r="K5" t="n">
@@ -718,7 +718,7 @@
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>+0.51%</t>
+          <t>+0.54%</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -766,20 +766,20 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.15%247,000</t>
+          <t>4.42%221,000</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.15%</t>
+          <t>4.42%</t>
         </is>
       </c>
       <c r="K6" t="n">
-        <v>247000</v>
+        <v>221000</v>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>-0.09%</t>
+          <t>-0.08%</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -827,12 +827,12 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.25%238,000</t>
+          <t>4.38%238,000</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>4.25%</t>
+          <t>4.38%</t>
         </is>
       </c>
       <c r="K7" t="n">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -888,12 +888,12 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>4.10%154,000</t>
+          <t>3.97%154,000</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>4.10%</t>
+          <t>3.97%</t>
         </is>
       </c>
       <c r="K8" t="n">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -931,38 +931,38 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>3443創意</t>
+          <t>3017奇鋐</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-1.72%5995</t>
+          <t>-0.44%3410</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-1.72%</t>
+          <t>-0.44%</t>
         </is>
       </c>
       <c r="H9" t="n">
-        <v>5995</v>
+        <v>3410</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>4.03%190,000</t>
+          <t>3.90%336,000</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>4.03%</t>
+          <t>3.90%</t>
         </is>
       </c>
       <c r="K9" t="n">
-        <v>190000</v>
+        <v>336000</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>-0.07%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -992,38 +992,38 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>3017奇鋐</t>
+          <t>3443創意</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>-0.44%3410</t>
+          <t>-1.72%5995</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>-0.44%</t>
+          <t>-1.72%</t>
         </is>
       </c>
       <c r="H10" t="n">
-        <v>3410</v>
+        <v>5995</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>4.00%336,000</t>
+          <t>3.87%190,000</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>4.00%</t>
+          <t>3.87%</t>
         </is>
       </c>
       <c r="K10" t="n">
-        <v>336000</v>
+        <v>190000</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>-0.07%</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1071,12 +1071,12 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>3.20%470,000</t>
+          <t>3.25%470,000</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>3.20%</t>
+          <t>3.25%</t>
         </is>
       </c>
       <c r="K11" t="n">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1132,12 +1132,12 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.98%938,000</t>
+          <t>3.17%938,000</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>2.98%</t>
+          <t>3.17%</t>
         </is>
       </c>
       <c r="K12" t="n">
@@ -1145,7 +1145,7 @@
       </c>
       <c r="L12" t="inlineStr">
         <is>
-          <t>+0.25%</t>
+          <t>+0.27%</t>
         </is>
       </c>
       <c r="M12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1193,12 +1193,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2.93%52,400</t>
+          <t>3.05%52,400</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>2.93%</t>
+          <t>3.05%</t>
         </is>
       </c>
       <c r="K13" t="n">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1236,38 +1236,38 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>2308台達電</t>
+          <t>3037欣興</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>+1.36%1865</t>
+          <t>-2.8%971</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>+1.36%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="H14" t="n">
-        <v>1865</v>
+        <v>971</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>2.85%446,000</t>
+          <t>3.00%907,000</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>2.85%</t>
+          <t>3.00%</t>
         </is>
       </c>
       <c r="K14" t="n">
-        <v>446000</v>
+        <v>907000</v>
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>-0.09%</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1297,38 +1297,38 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>6187萬 潤</t>
+          <t>2308台達電</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>+2.23%1375</t>
+          <t>+1.36%1865</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>+2.23%</t>
+          <t>+1.36%</t>
         </is>
       </c>
       <c r="H15" t="n">
-        <v>1375</v>
+        <v>1865</v>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2.79%596,000</t>
+          <t>2.83%446,000</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>2.79%</t>
+          <t>2.83%</t>
         </is>
       </c>
       <c r="K15" t="n">
-        <v>596000</v>
+        <v>446000</v>
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>+0.06%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:52</t>
+          <t>2026-09-01 17:55:47</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1358,38 +1358,38 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3037欣興</t>
+          <t>6187萬 潤</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>-2.8%971</t>
+          <t>+2.23%1375</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>+2.23%</t>
         </is>
       </c>
       <c r="H16" t="n">
-        <v>971</v>
+        <v>1375</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>2.15%620,000</t>
+          <t>2.79%596,000</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>2.15%</t>
+          <t>2.79%</t>
         </is>
       </c>
       <c r="K16" t="n">
-        <v>620000</v>
+        <v>596000</v>
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>-0.06%</t>
+          <t>+0.06%</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1419,38 +1419,38 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6274台 燿</t>
+          <t>2383台光電</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>+1.05%1450</t>
+          <t>+2.83%5640</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>+1.05%</t>
+          <t>+2.83%</t>
         </is>
       </c>
       <c r="H17" t="n">
-        <v>1450</v>
+        <v>5640</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1.97%395,000</t>
+          <t>2.36%123,000</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>1.97%</t>
+          <t>2.36%</t>
         </is>
       </c>
       <c r="K17" t="n">
-        <v>395000</v>
+        <v>123000</v>
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1480,34 +1480,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>3044健鼎</t>
+          <t>6274台 燿</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>+1.31%503</t>
+          <t>+1.05%1450</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>+1.31%</t>
+          <t>+1.05%</t>
         </is>
       </c>
       <c r="H18" t="n">
-        <v>503</v>
+        <v>1450</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1.79%1,034,000</t>
+          <t>1.95%395,000</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1.79%</t>
+          <t>1.95%</t>
         </is>
       </c>
       <c r="K18" t="n">
-        <v>1034000</v>
+        <v>395000</v>
       </c>
       <c r="L18" t="inlineStr">
         <is>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1541,38 +1541,38 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>2345智邦</t>
+          <t>3665貿聯-KY</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>+8.35%2205</t>
+          <t>+6.68%2315</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>+8.35%</t>
+          <t>+6.68%</t>
         </is>
       </c>
       <c r="H19" t="n">
-        <v>2205</v>
+        <v>2315</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1.61%227,000</t>
+          <t>1.80%228,000</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>1.61%</t>
+          <t>1.80%</t>
         </is>
       </c>
       <c r="K19" t="n">
-        <v>227000</v>
+        <v>228000</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>+0.13%</t>
+          <t>+0.12%</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1602,38 +1602,38 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>1303南亞</t>
+          <t>3044健鼎</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>-3.3%234.5</t>
+          <t>+1.31%503</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>-3.3%</t>
+          <t>+1.31%</t>
         </is>
       </c>
       <c r="H20" t="n">
-        <v>234.5</v>
+        <v>503</v>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1.57%1,861,000</t>
+          <t>1.77%1,034,000</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1.57%</t>
+          <t>1.77%</t>
         </is>
       </c>
       <c r="K20" t="n">
-        <v>1861000</v>
+        <v>1034000</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>-0.05%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1663,38 +1663,38 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>2881富邦金</t>
+          <t>2345智邦</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>+0.69%145</t>
+          <t>+8.35%2205</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>+0.69%</t>
+          <t>+8.35%</t>
         </is>
       </c>
       <c r="H21" t="n">
-        <v>145</v>
+        <v>2205</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>1.55%3,104,000</t>
+          <t>1.70%227,000</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>1.55%</t>
+          <t>1.70%</t>
         </is>
       </c>
       <c r="K21" t="n">
-        <v>3104000</v>
+        <v>227000</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>+0.13%</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1724,38 +1724,38 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>2383台光電</t>
+          <t>2881富邦金</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>+2.83%5640</t>
+          <t>+0.69%145</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>+2.83%</t>
+          <t>+0.69%</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>5640</v>
+        <v>145</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>1.45%76,000</t>
+          <t>1.53%3,104,000</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1.45%</t>
+          <t>1.53%</t>
         </is>
       </c>
       <c r="K22" t="n">
-        <v>76000</v>
+        <v>3104000</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1785,38 +1785,38 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2368金像電</t>
+          <t>1303南亞</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>+5.15%1225</t>
+          <t>-3.3%234.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>+5.15%</t>
+          <t>-3.3%</t>
         </is>
       </c>
       <c r="H23" t="n">
-        <v>1225</v>
+        <v>234.5</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>1.43%353,000</t>
+          <t>1.48%1,861,000</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.48%</t>
         </is>
       </c>
       <c r="K23" t="n">
-        <v>353000</v>
+        <v>1861000</v>
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>-0.05%</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1846,38 +1846,38 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>2885元大金</t>
+          <t>2368金像電</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>+1.99%66.7</t>
+          <t>+5.15%1225</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>+1.99%</t>
+          <t>+5.15%</t>
         </is>
       </c>
       <c r="H24" t="n">
-        <v>66.7</v>
+        <v>1225</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>1.43%6,267,040</t>
+          <t>1.47%353,000</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1.43%</t>
+          <t>1.47%</t>
         </is>
       </c>
       <c r="K24" t="n">
-        <v>6267040</v>
+        <v>353000</v>
       </c>
       <c r="L24" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.07%</t>
         </is>
       </c>
       <c r="M24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1907,38 +1907,38 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3665貿聯-KY</t>
+          <t>2885元大金</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>+6.68%2315</t>
+          <t>+1.99%66.7</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>+6.68%</t>
+          <t>+1.99%</t>
         </is>
       </c>
       <c r="H25" t="n">
-        <v>2315</v>
+        <v>66.7</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>1.27%168,000</t>
+          <t>1.42%6,267,040</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1.27%</t>
+          <t>1.42%</t>
         </is>
       </c>
       <c r="K25" t="n">
-        <v>168000</v>
+        <v>6267040</v>
       </c>
       <c r="L25" t="inlineStr">
         <is>
-          <t>+0.08%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1968,38 +1968,38 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>3036文曄</t>
+          <t>3529力旺</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>0%196</t>
+          <t>+10%2640</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>+10%</t>
         </is>
       </c>
       <c r="H26" t="n">
-        <v>196</v>
+        <v>2640</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>1.04%1,532,000</t>
+          <t>1.10%122,000</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.10%</t>
         </is>
       </c>
       <c r="K26" t="n">
-        <v>1532000</v>
+        <v>122000</v>
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.10%</t>
         </is>
       </c>
       <c r="M26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2029,38 +2029,38 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>3026禾伸堂</t>
+          <t>3036文曄</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>-1.48%731</t>
+          <t>0%196</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>0%</t>
         </is>
       </c>
       <c r="H27" t="n">
-        <v>731</v>
+        <v>196</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>1.04%404,000</t>
+          <t>1.02%1,532,000</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1.04%</t>
+          <t>1.02%</t>
         </is>
       </c>
       <c r="K27" t="n">
-        <v>404000</v>
+        <v>1532000</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
-          <t>-0.02%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2090,38 +2090,38 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3529力旺</t>
+          <t>3026禾伸堂</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>+10%2640</t>
+          <t>-1.48%731</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>+10%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H28" t="n">
-        <v>2640</v>
+        <v>731</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>1.02%122,000</t>
+          <t>1.00%404,000</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1.02%</t>
+          <t>1.00%</t>
         </is>
       </c>
       <c r="K28" t="n">
-        <v>122000</v>
+        <v>404000</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
-          <t>+0.10%</t>
+          <t>-0.02%</t>
         </is>
       </c>
       <c r="M28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2151,38 +2151,38 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3081聯 亞</t>
+          <t>7750新 代</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>-2.97%3425</t>
+          <t>+3.3%2345</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>-2.97%</t>
+          <t>+3.3%</t>
         </is>
       </c>
       <c r="H29" t="n">
-        <v>3425</v>
+        <v>2345</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>1.01%82,000</t>
+          <t>0.97%122,000</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1.01%</t>
+          <t>0.97%</t>
         </is>
       </c>
       <c r="K29" t="n">
-        <v>82000</v>
+        <v>122000</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
-          <t>-0.03%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2212,25 +2212,25 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>7750新 代</t>
+          <t>3711日月光投控</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>+3.3%2345</t>
+          <t>+4.45%610</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+3.3%</t>
+          <t>+4.45%</t>
         </is>
       </c>
       <c r="H30" t="n">
-        <v>2345</v>
+        <v>610</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>0.96%122,000</t>
+          <t>0.96%464,000</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2239,11 +2239,11 @@
         </is>
       </c>
       <c r="K30" t="n">
-        <v>122000</v>
+        <v>464000</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.04%</t>
         </is>
       </c>
       <c r="M30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:54</t>
+          <t>2026-09-01 17:55:48</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2273,25 +2273,25 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>2313華通</t>
+          <t>3081聯 亞</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>+1.41%252</t>
+          <t>-2.97%3425</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>+1.41%</t>
+          <t>-2.97%</t>
         </is>
       </c>
       <c r="H31" t="n">
-        <v>252</v>
+        <v>3425</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>0.96%1,107,336</t>
+          <t>0.96%82,000</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2300,11 +2300,11 @@
         </is>
       </c>
       <c r="K31" t="n">
-        <v>1107336</v>
+        <v>82000</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
-          <t>+0.01%</t>
+          <t>-0.03%</t>
         </is>
       </c>
       <c r="M31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2334,38 +2334,38 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>3711日月光投控</t>
+          <t>2313華通</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>+4.45%610</t>
+          <t>+1.41%252</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>+4.45%</t>
+          <t>+1.41%</t>
         </is>
       </c>
       <c r="H32" t="n">
-        <v>610</v>
+        <v>252</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>0.94%464,000</t>
+          <t>0.95%1,107,336</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K32" t="n">
-        <v>464000</v>
+        <v>1107336</v>
       </c>
       <c r="L32" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.01%</t>
         </is>
       </c>
       <c r="M32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2395,38 +2395,38 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>2303聯電</t>
+          <t>2449京元電子</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>+2.71%132.5</t>
+          <t>+8.56%279</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>+2.71%</t>
+          <t>+8.56%</t>
         </is>
       </c>
       <c r="H33" t="n">
-        <v>132.5</v>
+        <v>279</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>0.94%2,096,000</t>
+          <t>0.95%999,000</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>0.94%</t>
+          <t>0.95%</t>
         </is>
       </c>
       <c r="K33" t="n">
-        <v>2096000</v>
+        <v>999000</v>
       </c>
       <c r="L33" t="inlineStr">
         <is>
-          <t>+0.03%</t>
+          <t>+0.08%</t>
         </is>
       </c>
       <c r="M33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2456,38 +2456,38 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>6442光 聖</t>
+          <t>2303聯電</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>+0.31%1635</t>
+          <t>+2.71%132.5</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>+0.31%</t>
+          <t>+2.71%</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>1635</v>
+        <v>132.5</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>0.92%163,000</t>
+          <t>0.94%2,096,000</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>0.92%</t>
+          <t>0.94%</t>
         </is>
       </c>
       <c r="K34" t="n">
-        <v>163000</v>
+        <v>2096000</v>
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>+0.03%</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2517,38 +2517,38 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>2449京元電子</t>
+          <t>6442光 聖</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>+8.56%279</t>
+          <t>+0.31%1635</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>+8.56%</t>
+          <t>+0.31%</t>
         </is>
       </c>
       <c r="H35" t="n">
-        <v>279</v>
+        <v>1635</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>0.89%999,000</t>
+          <t>0.91%163,000</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>0.89%</t>
+          <t>0.91%</t>
         </is>
       </c>
       <c r="K35" t="n">
-        <v>999000</v>
+        <v>163000</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
-          <t>+0.07%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2596,12 +2596,12 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>0.83%960,000</t>
+          <t>0.84%960,000</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>0.83%</t>
+          <t>0.84%</t>
         </is>
       </c>
       <c r="K36" t="n">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2657,12 +2657,12 @@
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>0.78%664,000</t>
+          <t>0.77%664,000</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
         <is>
-          <t>0.78%</t>
+          <t>0.77%</t>
         </is>
       </c>
       <c r="K37" t="n">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2761,38 +2761,38 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>7769鴻 勁</t>
+          <t>4979華星光</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>+0.17%5870</t>
+          <t>-1.48%600</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+0.17%</t>
+          <t>-1.48%</t>
         </is>
       </c>
       <c r="H39" t="n">
-        <v>5870</v>
+        <v>600</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>0.69%34,000</t>
+          <t>0.60%293,000</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>0.69%</t>
+          <t>0.60%</t>
         </is>
       </c>
       <c r="K39" t="n">
-        <v>34000</v>
+        <v>293000</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
-          <t>+0.00%</t>
+          <t>-0.01%</t>
         </is>
       </c>
       <c r="M39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2822,38 +2822,38 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4979華星光</t>
+          <t>6515穎崴</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>-1.48%600</t>
+          <t>+9.94%6910</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>-1.48%</t>
+          <t>+9.94%</t>
         </is>
       </c>
       <c r="H40" t="n">
-        <v>600</v>
+        <v>6910</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>0.62%293,000</t>
+          <t>0.49%21,000</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
         <is>
-          <t>0.62%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K40" t="n">
-        <v>293000</v>
+        <v>21000</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
-          <t>-0.01%</t>
+          <t>+0.05%</t>
         </is>
       </c>
       <c r="M40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2901,12 +2901,12 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>0.50%340,000</t>
+          <t>0.49%340,000</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>0.50%</t>
+          <t>0.49%</t>
         </is>
       </c>
       <c r="K41" t="n">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2944,38 +2944,38 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>6515穎崴</t>
+          <t>7769鴻 勁</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>+9.94%6910</t>
+          <t>+0.17%5870</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>+9.94%</t>
+          <t>+0.17%</t>
         </is>
       </c>
       <c r="H42" t="n">
-        <v>6910</v>
+        <v>5870</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>0.46%21,000</t>
+          <t>0.40%20,000</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>0.46%</t>
+          <t>0.40%</t>
         </is>
       </c>
       <c r="K42" t="n">
-        <v>21000</v>
+        <v>20000</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
-          <t>+0.04%</t>
+          <t>+0.00%</t>
         </is>
       </c>
       <c r="M42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3005,38 +3005,38 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>3090日電貿</t>
+          <t>5434崇越</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>-1.14%173</t>
+          <t>+4.85%540</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>-1.14%</t>
+          <t>+4.85%</t>
         </is>
       </c>
       <c r="H43" t="n">
-        <v>173</v>
+        <v>540</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>0.36%592,000</t>
+          <t>0.37%200,000</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.37%</t>
         </is>
       </c>
       <c r="K43" t="n">
-        <v>592000</v>
+        <v>200000</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
-          <t>-0.00%</t>
+          <t>+0.02%</t>
         </is>
       </c>
       <c r="M43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3066,38 +3066,38 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5434崇越</t>
+          <t>3090日電貿</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>+4.85%540</t>
+          <t>-1.14%173</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>+4.85%</t>
+          <t>-1.14%</t>
         </is>
       </c>
       <c r="H44" t="n">
-        <v>540</v>
+        <v>173</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>0.36%200,000</t>
+          <t>0.35%592,000</t>
         </is>
       </c>
       <c r="J44" t="inlineStr">
         <is>
-          <t>0.36%</t>
+          <t>0.35%</t>
         </is>
       </c>
       <c r="K44" t="n">
-        <v>200000</v>
+        <v>592000</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
-          <t>+0.02%</t>
+          <t>-0.00%</t>
         </is>
       </c>
       <c r="M44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3145,12 +3145,12 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>0.34%133,000</t>
+          <t>0.32%133,000</t>
         </is>
       </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>0.34%</t>
+          <t>0.32%</t>
         </is>
       </c>
       <c r="K45" t="n">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 16:18:55</t>
+          <t>2026-09-01 17:55:49</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -3206,12 +3206,12 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>0.32%115,000</t>
+          <t>0.31%115,000</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>0.32%</t>
+          <t>0.31%</t>
         </is>
       </c>
       <c r="K46" t="n">

--- a/etf_holdings/2026-09-01_00400A_full_holdings.xlsx
+++ b/etf_holdings/2026-09-01_00400A_full_holdings.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -552,7 +552,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -613,7 +613,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -735,7 +735,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -796,7 +796,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -857,7 +857,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -918,7 +918,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -1040,7 +1040,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -1101,7 +1101,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -1284,7 +1284,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -1345,7 +1345,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:47</t>
+          <t>2026-09-01 19:40:22</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -1467,7 +1467,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -1528,7 +1528,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -1589,7 +1589,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1650,7 +1650,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -1772,7 +1772,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -1833,7 +1833,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1955,7 +1955,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2077,7 +2077,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -2138,7 +2138,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -2199,7 +2199,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -2260,7 +2260,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:48</t>
+          <t>2026-09-01 19:40:24</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -2443,7 +2443,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -2504,7 +2504,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -2565,7 +2565,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -2626,7 +2626,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -2687,7 +2687,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -2809,7 +2809,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -2870,7 +2870,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -2992,7 +2992,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -3053,7 +3053,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -3175,7 +3175,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>2026-09-01 17:55:49</t>
+          <t>2026-09-01 19:40:25</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
